--- a/Documentation/Event log.xlsx
+++ b/Documentation/Event log.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hr\Documents\01_Low tech to the people\01_Fizzy-ball\Hardware\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46688F3B-7268-4232-9C89-A7431EC7C182}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2E9AA38-AA57-4D77-9EDD-81EEC1FE09F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Setup 1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="82">
   <si>
     <t>PCB</t>
   </si>
@@ -260,6 +260,24 @@
   </si>
   <si>
     <t>may + june</t>
+  </si>
+  <si>
+    <t>In the end not used by the BEP group</t>
+  </si>
+  <si>
+    <t>screw to the motor got loose (the one that is inside the pulley, after re assembling it worked again</t>
+  </si>
+  <si>
+    <t>Added a small wooden stick to the battery holder to clamp down the battery. This worked well.</t>
+  </si>
+  <si>
+    <t>The motor pulley connection with the screw broke off. Fixed it by using the two holes in the pulley to connect to the motor connector and then to the motor</t>
+  </si>
+  <si>
+    <t>Took the drivetrain apart to test with new CFMs: the pulley is now very close to the pcb, setscrew has to be tightend before turning the pulley</t>
+  </si>
+  <si>
+    <t>Size of the o-ring is now 23mm, don't know if it has been stretched to this length or that it stayed that way</t>
   </si>
 </sst>
 </file>
@@ -607,7 +625,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P16"/>
+  <dimension ref="A1:P17"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8.81640625" bestFit="1" customWidth="1"/>
@@ -850,6 +868,11 @@
         <v>74</v>
       </c>
     </row>
+    <row r="17" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C17" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="M1:P1"/>
@@ -864,7 +887,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDD0F91A-F783-4752-993A-8BA625570F2E}">
-  <dimension ref="A1:O12"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="11.7265625" customWidth="1"/>
@@ -1091,6 +1114,22 @@
         <v>70</v>
       </c>
     </row>
+    <row r="13" spans="1:15" ht="58" x14ac:dyDescent="0.35">
+      <c r="B13" s="2">
+        <v>46171</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="B14" s="2">
+        <v>46171</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="D1:E1"/>
@@ -1105,7 +1144,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{953EE5A4-2208-48A0-821E-5376883CB974}">
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:P14"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16" bestFit="1" customWidth="1"/>
@@ -1357,6 +1396,30 @@
       </c>
       <c r="J11" t="s">
         <v>73</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="B12" s="2">
+        <v>46169</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="B13" s="2">
+        <v>46190</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="58" x14ac:dyDescent="0.35">
+      <c r="B14" s="2">
+        <v>46190</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>80</v>
       </c>
     </row>
   </sheetData>
